--- a/research/traditional_assets/database/data/sudan/sudan_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/sudan/sudan_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.6</v>
+        <v>1.192</v>
       </c>
       <c r="E2">
-        <v>1.37</v>
+        <v>0.88</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,10 +606,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>12</v>
+        <v>4.57</v>
       </c>
       <c r="L2">
-        <v>3.26975476839237</v>
+        <v>0.270414201183432</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,31 +633,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>27.8</v>
+        <v>36.9</v>
       </c>
       <c r="V2">
-        <v>0.4982078853046595</v>
+        <v>1.142414860681115</v>
       </c>
       <c r="W2">
-        <v>0.1967213114754098</v>
+        <v>0.1294617563739377</v>
       </c>
       <c r="X2">
-        <v>0.1589427176349829</v>
+        <v>0.174446824102096</v>
       </c>
       <c r="Y2">
-        <v>0.03777859384042689</v>
+        <v>-0.04498506772815827</v>
       </c>
       <c r="Z2">
-        <v>0.1301418439716312</v>
+        <v>2.253333333333334</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1589427176349829</v>
+        <v>0.174446824102096</v>
       </c>
       <c r="AC2">
-        <v>-0.1589427176349829</v>
+        <v>-0.174446824102096</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -669,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-27.8</v>
+        <v>-36.9</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -678,10 +678,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.992857142857143</v>
+        <v>8.02173913043478</v>
       </c>
       <c r="AK2">
-        <v>-3.706666666666668</v>
+        <v>12.3</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.6</v>
+        <v>1.192</v>
       </c>
       <c r="E3">
-        <v>1.37</v>
+        <v>0.88</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>4.57</v>
       </c>
       <c r="L3">
-        <v>3.26975476839237</v>
+        <v>0.270414201183432</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,31 +752,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>27.8</v>
+        <v>36.9</v>
       </c>
       <c r="V3">
-        <v>0.4982078853046595</v>
+        <v>1.142414860681115</v>
       </c>
       <c r="W3">
-        <v>0.1967213114754098</v>
+        <v>0.1294617563739377</v>
       </c>
       <c r="X3">
-        <v>0.1589427176349829</v>
+        <v>0.174446824102096</v>
       </c>
       <c r="Y3">
-        <v>0.03777859384042689</v>
+        <v>-0.04498506772815827</v>
       </c>
       <c r="Z3">
-        <v>0.1301418439716312</v>
+        <v>2.253333333333334</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1589427176349829</v>
+        <v>0.174446824102096</v>
       </c>
       <c r="AC3">
-        <v>-0.1589427176349829</v>
+        <v>-0.174446824102096</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -788,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-27.8</v>
+        <v>-36.9</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -797,10 +797,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.992857142857143</v>
+        <v>8.02173913043478</v>
       </c>
       <c r="AK3">
-        <v>-3.706666666666668</v>
+        <v>12.3</v>
       </c>
       <c r="AL3">
         <v>0</v>
